--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -94,55 +94,28 @@
     <t>Ground_01</t>
   </si>
   <si>
-    <t>1;5</t>
-  </si>
-  <si>
-    <t>Q1;50|Q2;50|Q3;10|Q4;10|Q5;10|Q6;10|Q7;10|Q8;10|Q9;10|Q10;10|Q11;10|Q12;10|Q13;50|Q14;50|Q15;50|Q16;50|Q17;50|Q18;50|Q19;50|Q20;50</t>
+    <t>2;2</t>
+  </si>
+  <si>
+    <t>Q1;50|Q2;10|Q3;10</t>
   </si>
   <si>
     <t>Dig_02</t>
   </si>
   <si>
-    <t>6;1</t>
+    <t>2;3</t>
+  </si>
+  <si>
+    <t>Q1;100|Q2;30|Q3;30|Q4;30|Q5;20|Q6;20|Q7;10|Q8;10|Q9;10</t>
   </si>
   <si>
     <t>Dig_03</t>
   </si>
   <si>
-    <t>4;2</t>
-  </si>
-  <si>
-    <t>Dig_04</t>
-  </si>
-  <si>
-    <t>5;1</t>
-  </si>
-  <si>
-    <t>Dig_05</t>
-  </si>
-  <si>
-    <t>6;2</t>
-  </si>
-  <si>
-    <t>Dig_06</t>
-  </si>
-  <si>
-    <t>4;1</t>
-  </si>
-  <si>
-    <t>Dig_07</t>
-  </si>
-  <si>
-    <t>5;2</t>
-  </si>
-  <si>
-    <t>Dig_08</t>
-  </si>
-  <si>
-    <t>Dig_09</t>
-  </si>
-  <si>
-    <t>Dig_10</t>
+    <t>2;4</t>
+  </si>
+  <si>
+    <t>Q1;100|Q2;30|Q3;30|Q10;30|Q11;20|Q12;20|Q13;20|Q14;20|Q15;20</t>
   </si>
 </sst>
 </file>
@@ -308,7 +281,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +291,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +617,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,16 +641,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -680,91 +659,92 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1111,8 +1091,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="14.25" customWidth="1"/>
   </cols>
@@ -1193,7 +1173,7 @@
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1213,13 +1193,13 @@
       <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -1231,150 +1211,10 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-      <c r="D8">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>50</v>
-      </c>
-      <c r="D9">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10">
-        <v>50</v>
-      </c>
-      <c r="D10">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11">
-        <v>50</v>
-      </c>
-      <c r="D11">
-        <v>19</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>50</v>
-      </c>
-      <c r="D12">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13">
-        <v>50</v>
-      </c>
-      <c r="D13">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
@@ -31,6 +31,38 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>JM</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>JM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+挖坟_坟墓品质定义表_Dig_GraveQualityConfig</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
@@ -128,7 +160,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +311,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1220,5 +1263,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -135,6 +135,9 @@
     <t>Dig_02</t>
   </si>
   <si>
+    <t>Ground_02</t>
+  </si>
+  <si>
     <t>2;3</t>
   </si>
   <si>
@@ -142,6 +145,9 @@
   </si>
   <si>
     <t>Dig_03</t>
+  </si>
+  <si>
+    <t>Ground_03</t>
   </si>
   <si>
     <t>2;4</t>
@@ -1135,9 +1141,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="14.2545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1225,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -1234,18 +1240,18 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -1254,10 +1260,10 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_挖坟配置表_Dig_DigGameplayConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
     <t>2;2</t>
   </si>
   <si>
-    <t>Q1;50|Q2;10|Q3;10</t>
+    <t>Q101;10|Q1;50|Q2;10|Q3;10</t>
   </si>
   <si>
     <t>Dig_02</t>
@@ -141,7 +141,7 @@
     <t>2;3</t>
   </si>
   <si>
-    <t>Q1;100|Q2;30|Q3;30|Q4;30|Q5;20|Q6;20|Q7;10|Q8;10|Q9;10</t>
+    <t>Q101;10|Q1;100|Q2;30|Q3;30|Q4;30|Q5;20|Q6;20|Q7;10|Q8;10|Q9;10</t>
   </si>
   <si>
     <t>Dig_03</t>
@@ -153,7 +153,7 @@
     <t>2;4</t>
   </si>
   <si>
-    <t>Q1;100|Q2;30|Q3;30|Q10;30|Q11;20|Q12;20|Q13;20|Q14;20|Q15;20</t>
+    <t>Q101;10|Q1;100|Q2;30|Q3;30|Q10;30|Q11;20|Q12;20|Q13;20|Q14;20|Q15;20</t>
   </si>
 </sst>
 </file>
@@ -319,12 +319,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -790,9 +790,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1143,7 +1149,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="11.6363636363636" customWidth="1"/>
     <col min="2" max="2" width="14.2545454545455" customWidth="1"/>
+    <col min="3" max="3" width="9.54545454545454" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="25.3636363636364" customWidth="1"/>
+    <col min="6" max="6" width="25.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1153,7 +1164,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1173,7 +1184,7 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
@@ -1193,7 +1204,7 @@
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1213,16 +1224,16 @@
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4">
-        <v>50</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="2">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2">
         <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1233,16 +1244,16 @@
       <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="2">
+        <v>40</v>
+      </c>
+      <c r="D5" s="2">
         <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1253,16 +1264,16 @@
       <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="2">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2">
         <v>14</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
